--- a/dataset/captions.xlsx
+++ b/dataset/captions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Semester5\Machine Learning\Project_ImageDescription\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{944D8F12-E1EC-4270-9699-4729A339420F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348AD93B-CE4E-4E35-BAE3-AE9059CD90BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{22E05C19-D6AE-4025-93B8-2E41A94C5A98}"/>
   </bookViews>
